--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-ballot</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:44:45+00:00</t>
+    <t>2024-03-25T10:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:59:40+00:00</t>
+    <t>2024-03-25T11:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T08:02:06+00:00</t>
+    <t>2024-05-23T12:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:05:52+00:00</t>
+    <t>2024-05-23T12:32:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:32:02+00:00</t>
+    <t>2024-05-23T14:35:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T14:35:00+00:00</t>
+    <t>2024-06-11T15:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:12+00:00</t>
+    <t>2024-06-11T15:33:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:34+00:00</t>
+    <t>2024-07-02T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(WORK))</t>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-08T11:39:28+00:00</t>
+    <t>2024-07-17T12:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T12:13:27+00:00</t>
+    <t>2024-07-17T14:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T14:21:13+00:00</t>
+    <t>2024-07-17T15:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T15:15:49+00:00</t>
+    <t>2024-07-17T15:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T07:11:02+00:00</t>
+    <t>2024-07-25T15:28:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:28:42+00:00</t>
+    <t>2024-07-25T15:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:29:18+00:00</t>
+    <t>2024-07-25T15:44:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:44:10+00:00</t>
+    <t>2024-08-01T13:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0-ballot</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-03T15:38:30+00:00</t>
+    <t>2024-09-04T07:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T07:28:39+00:00</t>
+    <t>2024-09-04T07:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-06T12:53:53+00:00</t>
+    <t>2024-10-28T08:07:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -422,7 +422,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -442,7 +442,7 @@
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:07:18+00:00</t>
+    <t>2024-10-28T08:08:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:08:30+00:00</t>
+    <t>2024-10-29T10:42:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:05:50+00:00</t>
+    <t>2025-01-28T09:07:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:07:36+00:00</t>
+    <t>2025-02-04T08:51:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T08:51:44+00:00</t>
+    <t>2025-02-04T09:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T09:30:35+00:00</t>
+    <t>2025-02-19T13:47:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:47:59+00:00</t>
+    <t>2025-02-19T13:52:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:52:01+00:00</t>
+    <t>2025-02-19T13:53:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:53:58+00:00</t>
+    <t>2025-02-19T13:58:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -636,7 +636,9 @@
     <t>FR Core Service Type Duration Extension</t>
   </si>
   <si>
-    <t>This French extension allows to associate the type of service with the duration of this service | Cette extension française permet d'associer le type de service avec la durée de ce service.</t>
+    <t>Cette extension française permet d'associer le type de service avec la durée de ce service.
++This French extension allows to associate the type of service with the duration of this service</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -656,7 +658,9 @@
     <t>FR Core Schedule availability time Extension</t>
   </si>
   <si>
-    <t>This extension specifies a list of periods of time (recurrent or not). It specifies the type of Schedule (busy-unavailable|free), the identifier of the period, the period with a possibly recurrence rule, the date of creation of the period and the priority of this period | Cette extension permet de préciser une liste de période de temps (récurrentes ou non). Elle spécifie le type de Schedule (busy-unavailable|free), l'identifiant de la période, la période (récurrente ou non avec une règle de récurrence dans le cas d'une période récurrente, la date de création de la période et une priorité.</t>
+    <t>Cette extension permet de préciser une liste de période de temps (récurrentes ou non). Elle spécifie le type de Schedule, l'identifiant de la période, la période (récurrente ou non avec une règle de récurrence dans le cas d'une période récurrente, la date de création de la période et une priorité.
++This extension specifies a list of periods of time (recurrent or not). It specifies the type of Schedule, the identifier of the period, the period with a possibly recurrence rule, the date of creation of the period and the priority of this period</t>
   </si>
   <si>
     <t>Schedule.modifierExtension</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:58:46+00:00</t>
+    <t>2025-02-19T14:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T14:07:54+00:00</t>
+    <t>2025-02-19T14:26:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T08:11:18+00:00</t>
+    <t>2025-05-20T13:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:27:17+00:00</t>
+    <t>2025-05-20T13:29:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:29:42+00:00</t>
+    <t>2025-05-20T13:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:48:39+00:00</t>
+    <t>2025-06-04T13:32:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-04T13:32:30+00:00</t>
+    <t>2025-06-24T17:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T17:01:22+00:00</t>
+    <t>2025-07-04T12:19:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04T12:19:33+00:00</t>
+    <t>2025-07-08T13:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-08T13:28:39+00:00</t>
+    <t>2025-07-16T09:34:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T09:34:35+00:00</t>
+    <t>2025-07-30T14:55:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-30T14:55:53+00:00</t>
+    <t>2025-10-08T07:32:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T07:32:57+00:00</t>
+    <t>2025-10-08T12:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T12:04:30+00:00</t>
+    <t>2025-10-08T16:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:25:45+00:00</t>
+    <t>2026-02-04T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T13:09:39+00:00</t>
+    <t>2026-02-09T06:47:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T06:47:58+00:00</t>
+    <t>2026-02-11T16:15:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T16:15:37+00:00</t>
+    <t>2026-02-17T10:02:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T10:02:14+00:00</t>
+    <t>2026-02-23T09:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T09:26:22+00:00</t>
+    <t>2026-02-23T10:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T10:39:10+00:00</t>
+    <t>2026-02-23T12:56:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T07:09:47+00:00</t>
+    <t>2026-03-25T10:22:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:11+00:00</t>
+    <t>2026-03-25T10:22:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:40+00:00</t>
+    <t>2026-03-25T10:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:25:13+00:00</t>
+    <t>2026-03-25T15:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T15:00:47+00:00</t>
+    <t>2026-03-31T09:16:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T09:16:18+00:00</t>
+    <t>2026-05-07T06:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:50:40+00:00</t>
+    <t>2026-05-27T14:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:53:55+00:00</t>
+    <t>2026-05-28T14:22:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:22:24+00:00</t>
+    <t>2026-06-12T14:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:04:24+00:00</t>
+    <t>2026-06-12T14:05:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:05:00+00:00</t>
+    <t>2026-06-12T14:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:35:23+00:00</t>
+    <t>2026-06-26T12:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T12:32:04+00:00</t>
+    <t>2026-06-29T09:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T09:30:52+00:00</t>
+    <t>2026-07-22T12:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:21:07+00:00</t>
+    <t>2026-07-27T15:02:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:02:31+00:00</t>
+    <t>2026-08-03T12:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T12:52:25+00:00</t>
+    <t>2026-08-04T12:22:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:22:31+00:00</t>
+    <t>2026-08-04T12:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-schedule.xlsx
+++ b/main/ig/StructureDefinition-fr-core-schedule.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:29:23+00:00</t>
+    <t>2026-08-10T16:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
